--- a/artfynd/A 9518-2022 artfynd.xlsx
+++ b/artfynd/A 9518-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9518-2022 artfynd.xlsx
+++ b/artfynd/A 9518-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120855328</v>
+        <v>120855309</v>
       </c>
       <c r="B3" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585467</v>
+        <v>585469</v>
       </c>
       <c r="R3" t="n">
-        <v>6345631</v>
+        <v>6345635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120855309</v>
+        <v>120855328</v>
       </c>
       <c r="B4" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585469</v>
+        <v>585467</v>
       </c>
       <c r="R4" t="n">
-        <v>6345635</v>
+        <v>6345631</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
